--- a/reports/一级子公司A_利润表_2026-09.xlsx
+++ b/reports/一级子公司A_利润表_2026-09.xlsx
@@ -2049,7 +2049,7 @@
         </is>
       </c>
       <c r="F3" s="13" t="n">
-        <v>185398719</v>
+        <v>188826011</v>
       </c>
       <c r="G3" s="13" t="n"/>
       <c r="I3" s="5" t="n"/>
@@ -2081,10 +2081,10 @@
         </is>
       </c>
       <c r="F4" s="14" t="n">
-        <v>180650801</v>
+        <v>179933355</v>
       </c>
       <c r="G4" s="14" t="n">
-        <v>1540607409</v>
+        <v>1540013726</v>
       </c>
       <c r="I4" s="5" t="n"/>
     </row>
@@ -2115,10 +2115,10 @@
         </is>
       </c>
       <c r="F5" s="14" t="n">
-        <v>735836</v>
+        <v>737424</v>
       </c>
       <c r="G5" s="14" t="n">
-        <v>6381480</v>
+        <v>6381326</v>
       </c>
     </row>
     <row r="6" ht="18" customHeight="1">
@@ -2148,10 +2148,10 @@
         </is>
       </c>
       <c r="F6" s="14" t="n">
-        <v>639520</v>
+        <v>640848</v>
       </c>
       <c r="G6" s="14" t="n">
-        <v>5535840</v>
+        <v>5538531</v>
       </c>
     </row>
     <row r="7" ht="18" customHeight="1">
@@ -2181,10 +2181,10 @@
         </is>
       </c>
       <c r="F7" s="14" t="n">
-        <v>540051</v>
+        <v>543558</v>
       </c>
       <c r="G7" s="14" t="n">
-        <v>4691138</v>
+        <v>4694840</v>
       </c>
     </row>
     <row r="8" ht="18" customHeight="1">
@@ -2214,10 +2214,10 @@
         </is>
       </c>
       <c r="F8" s="14" t="n">
-        <v>496625</v>
+        <v>500067</v>
       </c>
       <c r="G8" s="14" t="n">
-        <v>4316703</v>
+        <v>4319831</v>
       </c>
     </row>
     <row r="9" ht="18" customHeight="1">
@@ -2247,10 +2247,10 @@
         </is>
       </c>
       <c r="F9" s="14" t="n">
-        <v>270886</v>
+        <v>271516</v>
       </c>
       <c r="G9" s="14" t="n">
-        <v>2346007</v>
+        <v>2347714</v>
       </c>
     </row>
     <row r="10" ht="18" customHeight="1">
@@ -2280,10 +2280,10 @@
         </is>
       </c>
       <c r="F10" s="14" t="n">
-        <v>216547</v>
+        <v>216850</v>
       </c>
       <c r="G10" s="14" t="n">
-        <v>1876440</v>
+        <v>1877890</v>
       </c>
     </row>
     <row r="11" ht="18" customHeight="1">
@@ -2313,7 +2313,7 @@
         </is>
       </c>
       <c r="F11" s="13" t="n">
-        <v>182499254</v>
+        <v>185915748</v>
       </c>
       <c r="G11" s="13" t="n"/>
     </row>
@@ -2344,7 +2344,7 @@
         </is>
       </c>
       <c r="F12" s="13" t="n">
-        <v>177751336</v>
+        <v>177023092</v>
       </c>
       <c r="G12" s="13" t="n"/>
     </row>
@@ -2375,10 +2375,10 @@
         </is>
       </c>
       <c r="F13" s="14" t="n">
-        <v>74111949</v>
+        <v>73901360</v>
       </c>
       <c r="G13" s="14" t="n">
-        <v>750864297</v>
+        <v>751043607</v>
       </c>
     </row>
     <row r="14" ht="20.25" customHeight="1">
@@ -2408,10 +2408,10 @@
         </is>
       </c>
       <c r="F14" s="14" t="n">
-        <v>1675921</v>
+        <v>1668531</v>
       </c>
       <c r="G14" s="14" t="n">
-        <v>14543057</v>
+        <v>14537087</v>
       </c>
     </row>
     <row r="15" ht="18" customHeight="1">
@@ -2441,10 +2441,10 @@
         </is>
       </c>
       <c r="F15" s="14" t="n">
-        <v>1510440</v>
+        <v>1506125</v>
       </c>
       <c r="G15" s="14" t="n">
-        <v>13137302</v>
+        <v>13126375</v>
       </c>
     </row>
     <row r="16" ht="18" customHeight="1">
@@ -2474,10 +2474,10 @@
         </is>
       </c>
       <c r="F16" s="14" t="n">
-        <v>98647237</v>
+        <v>98136107</v>
       </c>
       <c r="G16" s="14" t="n">
-        <v>721241658</v>
+        <v>720487751</v>
       </c>
     </row>
     <row r="17" ht="18" customHeight="1">
@@ -2507,10 +2507,10 @@
         </is>
       </c>
       <c r="F17" s="14" t="n">
-        <v>1736429</v>
+        <v>1727539</v>
       </c>
       <c r="G17" s="14" t="n">
-        <v>15010849</v>
+        <v>15004825</v>
       </c>
     </row>
     <row r="18" ht="18" customHeight="1">
@@ -2540,10 +2540,10 @@
         </is>
       </c>
       <c r="F18" s="14" t="n">
-        <v>755093</v>
+        <v>756755</v>
       </c>
       <c r="G18" s="14" t="n">
-        <v>6567525</v>
+        <v>6565774</v>
       </c>
     </row>
     <row r="19" ht="18" customHeight="1">
@@ -2573,10 +2573,10 @@
         </is>
       </c>
       <c r="F19" s="14" t="n">
-        <v>2696989</v>
+        <v>2712055</v>
       </c>
       <c r="G19" s="14" t="n">
-        <v>23463618</v>
+        <v>23461806</v>
       </c>
     </row>
     <row r="20" ht="18" customHeight="1">
@@ -2606,10 +2606,10 @@
         </is>
       </c>
       <c r="F20" s="14" t="n">
-        <v>1192664</v>
+        <v>1193414</v>
       </c>
       <c r="G20" s="14" t="n">
-        <v>10322160</v>
+        <v>10323588</v>
       </c>
     </row>
     <row r="21" ht="18" customHeight="1">
@@ -2639,10 +2639,10 @@
         </is>
       </c>
       <c r="F21" s="14" t="n">
-        <v>4652890</v>
+        <v>4671492</v>
       </c>
       <c r="G21" s="14" t="n">
-        <v>40342718</v>
+        <v>40367469</v>
       </c>
     </row>
     <row r="22" ht="18" customHeight="1">
@@ -2672,10 +2672,10 @@
         </is>
       </c>
       <c r="F22" s="14" t="n">
-        <v>95028</v>
+        <v>93187</v>
       </c>
       <c r="G22" s="14" t="n">
-        <v>839973</v>
+        <v>834997</v>
       </c>
     </row>
     <row r="23" ht="18" customHeight="1">
@@ -2705,10 +2705,10 @@
         </is>
       </c>
       <c r="F23" s="14" t="n">
-        <v>0</v>
+        <v>2477968</v>
       </c>
       <c r="G23" s="14" t="n">
-        <v>0</v>
+        <v>21411544</v>
       </c>
     </row>
     <row r="24" ht="18" customHeight="1">
@@ -2738,10 +2738,10 @@
         </is>
       </c>
       <c r="F24" s="14" t="n">
-        <v>0</v>
+        <v>1650009</v>
       </c>
       <c r="G24" s="14" t="n">
-        <v>0</v>
+        <v>14273570</v>
       </c>
     </row>
     <row r="25" ht="18" customHeight="1">
@@ -2771,7 +2771,7 @@
         </is>
       </c>
       <c r="F25" s="13" t="n">
-        <v>128290893</v>
+        <v>136662849</v>
       </c>
       <c r="G25" s="13" t="n"/>
     </row>
@@ -2802,7 +2802,7 @@
         </is>
       </c>
       <c r="F26" s="13" t="n">
-        <v>115147376</v>
+        <v>114643598</v>
       </c>
       <c r="G26" s="13" t="n"/>
     </row>
@@ -2833,10 +2833,10 @@
         </is>
       </c>
       <c r="F27" s="14" t="n">
-        <v>112872929</v>
+        <v>112381499</v>
       </c>
       <c r="G27" s="14" t="n">
-        <v>952526929</v>
+        <v>952417558</v>
       </c>
     </row>
     <row r="28" ht="18" customHeight="1">
@@ -2866,10 +2866,10 @@
         </is>
       </c>
       <c r="F28" s="14" t="n">
-        <v>2274447</v>
+        <v>2262099</v>
       </c>
       <c r="G28" s="14" t="n">
-        <v>19702589</v>
+        <v>19697945</v>
       </c>
     </row>
     <row r="29" ht="18" customHeight="1">
@@ -2899,10 +2899,10 @@
         </is>
       </c>
       <c r="F29" s="14" t="n">
-        <v>0</v>
+        <v>4088693</v>
       </c>
       <c r="G29" s="14" t="n">
-        <v>0</v>
+        <v>35633236</v>
       </c>
     </row>
     <row r="30" ht="18" customHeight="1">
@@ -2932,10 +2932,10 @@
         </is>
       </c>
       <c r="F30" s="14" t="n">
-        <v>0</v>
+        <v>1308287</v>
       </c>
       <c r="G30" s="14" t="n">
-        <v>0</v>
+        <v>11400938</v>
       </c>
     </row>
     <row r="31" ht="18" customHeight="1">
@@ -2965,10 +2965,10 @@
         </is>
       </c>
       <c r="F31" s="14" t="n">
-        <v>0</v>
+        <v>818369</v>
       </c>
       <c r="G31" s="14" t="n">
-        <v>0</v>
+        <v>7125530</v>
       </c>
     </row>
     <row r="32" ht="18" customHeight="1">
@@ -2998,10 +2998,10 @@
         </is>
       </c>
       <c r="F32" s="14" t="n">
-        <v>0</v>
+        <v>983626</v>
       </c>
       <c r="G32" s="14" t="n">
-        <v>0</v>
+        <v>8551793</v>
       </c>
     </row>
     <row r="33" ht="18" customHeight="1">
@@ -3031,10 +3031,10 @@
         </is>
       </c>
       <c r="F33" s="14" t="n">
-        <v>0</v>
+        <v>739263</v>
       </c>
       <c r="G33" s="14" t="n">
-        <v>0</v>
+        <v>6415474</v>
       </c>
     </row>
     <row r="34" ht="18" customHeight="1">
@@ -3064,10 +3064,10 @@
         </is>
       </c>
       <c r="F34" s="14" t="n">
-        <v>0</v>
+        <v>493928</v>
       </c>
       <c r="G34" s="14" t="n">
-        <v>0</v>
+        <v>4278385</v>
       </c>
     </row>
     <row r="35" ht="18" customHeight="1">
@@ -3097,10 +3097,10 @@
         </is>
       </c>
       <c r="F35" s="14" t="n">
-        <v>0</v>
+        <v>412399</v>
       </c>
       <c r="G35" s="14" t="n">
-        <v>0</v>
+        <v>3566549</v>
       </c>
     </row>
     <row r="36" ht="18" customHeight="1">
@@ -3130,10 +3130,10 @@
         </is>
       </c>
       <c r="F36" s="14" t="n">
-        <v>1888865</v>
+        <v>1901749</v>
       </c>
       <c r="G36" s="14" t="n">
-        <v>16418906</v>
+        <v>16429954</v>
       </c>
     </row>
     <row r="37" ht="18" customHeight="1">
@@ -3163,10 +3163,10 @@
         </is>
       </c>
       <c r="F37" s="14" t="n">
-        <v>1457466</v>
+        <v>1467715</v>
       </c>
       <c r="G37" s="14" t="n">
-        <v>12669087</v>
+        <v>12677042</v>
       </c>
     </row>
     <row r="38" ht="18" customHeight="1">
@@ -3196,10 +3196,10 @@
         </is>
       </c>
       <c r="F38" s="14" t="n">
-        <v>1192523</v>
+        <v>1195434</v>
       </c>
       <c r="G38" s="14" t="n">
-        <v>10322308</v>
+        <v>10330149</v>
       </c>
     </row>
     <row r="39" ht="18" customHeight="1">
@@ -3229,10 +3229,10 @@
         </is>
       </c>
       <c r="F39" s="14" t="n">
-        <v>8984075</v>
+        <v>9008613</v>
       </c>
       <c r="G39" s="14" t="n">
-        <v>77870119</v>
+        <v>77940296</v>
       </c>
     </row>
     <row r="40" ht="18" customHeight="1">
@@ -3262,10 +3262,10 @@
         </is>
       </c>
       <c r="F40" s="14" t="n">
-        <v>369883</v>
+        <v>379223</v>
       </c>
       <c r="G40" s="14" t="n">
-        <v>3267132</v>
+        <v>3286043</v>
       </c>
     </row>
     <row r="41" ht="18" customHeight="1">
@@ -3295,10 +3295,10 @@
         </is>
       </c>
       <c r="F41" s="14" t="n">
-        <v>708171</v>
+        <v>689667</v>
       </c>
       <c r="G41" s="14" t="n">
-        <v>6251646</v>
+        <v>6211590</v>
       </c>
     </row>
     <row r="42" ht="18" customHeight="1">
@@ -3328,10 +3328,10 @@
         </is>
       </c>
       <c r="F42" s="14" t="n">
-        <v>805584</v>
+        <v>689667</v>
       </c>
       <c r="G42" s="14" t="n">
-        <v>7090173</v>
+        <v>6211590</v>
       </c>
     </row>
     <row r="43" ht="18" customHeight="1">
@@ -3361,10 +3361,10 @@
         </is>
       </c>
       <c r="F43" s="14" t="n">
-        <v>95188</v>
+        <v>92309</v>
       </c>
       <c r="G43" s="14" t="n">
-        <v>839843</v>
+        <v>833835</v>
       </c>
     </row>
     <row r="44" ht="18" customHeight="1">
@@ -3394,10 +3394,10 @@
         </is>
       </c>
       <c r="F44" s="14" t="n">
-        <v>0</v>
+        <v>350437</v>
       </c>
       <c r="G44" s="14" t="n">
-        <v>0</v>
+        <v>3167798</v>
       </c>
     </row>
     <row r="45" ht="18" customHeight="1">
@@ -3427,10 +3427,10 @@
         </is>
       </c>
       <c r="F45" s="14" t="n">
-        <v>0</v>
+        <v>715513</v>
       </c>
       <c r="G45" s="14" t="n">
-        <v>0</v>
+        <v>6234829</v>
       </c>
     </row>
     <row r="46" ht="18" customHeight="1">
@@ -3460,10 +3460,10 @@
         </is>
       </c>
       <c r="F46" s="14" t="n">
-        <v>0</v>
+        <v>233861</v>
       </c>
       <c r="G46" s="14" t="n">
-        <v>0</v>
+        <v>2111850</v>
       </c>
     </row>
     <row r="47" ht="18" customHeight="1">
@@ -3493,10 +3493,10 @@
         </is>
       </c>
       <c r="F47" s="14" t="n">
-        <v>0</v>
+        <v>175693</v>
       </c>
       <c r="G47" s="14" t="n">
-        <v>0</v>
+        <v>1584227</v>
       </c>
     </row>
     <row r="48" ht="18" customHeight="1">
@@ -3526,10 +3526,10 @@
         </is>
       </c>
       <c r="F48" s="14" t="n">
-        <v>0</v>
+        <v>293445</v>
       </c>
       <c r="G48" s="14" t="n">
-        <v>0</v>
+        <v>2641231</v>
       </c>
     </row>
     <row r="49" ht="18" customHeight="1">
@@ -3559,10 +3559,10 @@
         </is>
       </c>
       <c r="F49" s="14" t="n">
-        <v>0</v>
+        <v>1029304</v>
       </c>
       <c r="G49" s="14" t="n">
-        <v>0</v>
+        <v>8913714</v>
       </c>
     </row>
     <row r="50" ht="18" customHeight="1">
@@ -3592,10 +3592,10 @@
         </is>
       </c>
       <c r="F50" s="14" t="n">
-        <v>0</v>
+        <v>157138</v>
       </c>
       <c r="G50" s="14" t="n">
-        <v>0</v>
+        <v>1409671</v>
       </c>
     </row>
     <row r="51" ht="18" customHeight="1">
@@ -3625,10 +3625,10 @@
         </is>
       </c>
       <c r="F51" s="14" t="n">
-        <v>0</v>
+        <v>117997</v>
       </c>
       <c r="G51" s="14" t="n">
-        <v>0</v>
+        <v>1057544</v>
       </c>
     </row>
     <row r="52" ht="18" customHeight="1">
@@ -3658,10 +3658,10 @@
         </is>
       </c>
       <c r="F52" s="14" t="n">
-        <v>0</v>
+        <v>196729</v>
       </c>
       <c r="G52" s="14" t="n">
-        <v>0</v>
+        <v>1762828</v>
       </c>
     </row>
     <row r="53" ht="18" customHeight="1">
@@ -3691,10 +3691,10 @@
         </is>
       </c>
       <c r="F53" s="14" t="n">
-        <v>0</v>
+        <v>137632</v>
       </c>
       <c r="G53" s="14" t="n">
-        <v>0</v>
+        <v>1233971</v>
       </c>
     </row>
     <row r="54" ht="18" customHeight="1">
@@ -3724,10 +3724,10 @@
         </is>
       </c>
       <c r="F54" s="14" t="n">
-        <v>0</v>
+        <v>98171</v>
       </c>
       <c r="G54" s="14" t="n">
-        <v>0</v>
+        <v>881266</v>
       </c>
     </row>
     <row r="55" ht="18" customHeight="1">
@@ -3757,10 +3757,10 @@
         </is>
       </c>
       <c r="F55" s="14" t="n">
-        <v>0</v>
+        <v>78382</v>
       </c>
       <c r="G55" s="14" t="n">
-        <v>0</v>
+        <v>704815</v>
       </c>
     </row>
     <row r="56" ht="18" customHeight="1">
@@ -3790,10 +3790,10 @@
         </is>
       </c>
       <c r="F56" s="14" t="n">
-        <v>0</v>
+        <v>58657</v>
       </c>
       <c r="G56" s="14" t="n">
-        <v>0</v>
+        <v>528424</v>
       </c>
     </row>
     <row r="57" ht="18" customHeight="1">
@@ -3823,7 +3823,7 @@
         </is>
       </c>
       <c r="F57" s="13" t="n">
-        <v>54208361</v>
+        <v>51741922</v>
       </c>
       <c r="G57" s="13" t="n"/>
     </row>
@@ -3854,7 +3854,7 @@
         </is>
       </c>
       <c r="F58" s="13" t="n">
-        <v>63515969</v>
+        <v>58550477</v>
       </c>
       <c r="G58" s="13" t="n"/>
     </row>
@@ -3885,10 +3885,10 @@
         </is>
       </c>
       <c r="F59" s="14" t="n">
-        <v>0</v>
+        <v>408824</v>
       </c>
       <c r="G59" s="14" t="n">
-        <v>0</v>
+        <v>3563139</v>
       </c>
     </row>
     <row r="60" ht="18" customHeight="1">
@@ -3918,10 +3918,10 @@
         </is>
       </c>
       <c r="F60" s="14" t="n">
-        <v>0</v>
+        <v>97356</v>
       </c>
       <c r="G60" s="14" t="n">
-        <v>0</v>
+        <v>879873</v>
       </c>
     </row>
     <row r="61" ht="18" customHeight="1">
@@ -3951,10 +3951,10 @@
         </is>
       </c>
       <c r="F61" s="14" t="n">
-        <v>158510</v>
+        <v>153881</v>
       </c>
       <c r="G61" s="14" t="n">
-        <v>1399340</v>
+        <v>1389400</v>
       </c>
     </row>
     <row r="62" ht="18" customHeight="1">
@@ -3984,7 +3984,7 @@
         </is>
       </c>
       <c r="F62" s="13" t="n">
-        <v>54049851</v>
+        <v>51996865</v>
       </c>
       <c r="G62" s="13" t="n"/>
     </row>
@@ -4015,10 +4015,10 @@
         </is>
       </c>
       <c r="F63" s="14" t="n">
-        <v>5611850</v>
+        <v>5458599</v>
       </c>
       <c r="G63" s="14" t="n">
-        <v>49454872</v>
+        <v>49119853</v>
       </c>
     </row>
     <row r="64" ht="18" customHeight="1">
@@ -4048,7 +4048,7 @@
         </is>
       </c>
       <c r="F64" s="13" t="n">
-        <v>48438001</v>
+        <v>46538266</v>
       </c>
       <c r="G64" s="13" t="n"/>
     </row>
@@ -4108,7 +4108,7 @@
         </is>
       </c>
       <c r="F66" s="13" t="n">
-        <v>48438001</v>
+        <v>46538266</v>
       </c>
       <c r="G66" s="13" t="n"/>
     </row>
@@ -4201,7 +4201,7 @@
         </is>
       </c>
       <c r="F69" s="13" t="n">
-        <v>48438001</v>
+        <v>46538266</v>
       </c>
       <c r="G69" s="13" t="n"/>
     </row>
@@ -4410,7 +4410,7 @@
         </is>
       </c>
       <c r="F76" s="13" t="n">
-        <v>48438001</v>
+        <v>46538266</v>
       </c>
       <c r="G76" s="13" t="n"/>
     </row>
@@ -4441,7 +4441,7 @@
         </is>
       </c>
       <c r="F77" s="13" t="n">
-        <v>48438001</v>
+        <v>46538266</v>
       </c>
       <c r="G77" s="13" t="n"/>
     </row>
